--- a/PSP_providers_glossary_builder/data/input/PSP_rag_dataset.xlsx
+++ b/PSP_providers_glossary_builder/data/input/PSP_rag_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\glossary-builder-local-v7\PSP_providers_glossary_builder\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E6CD4A-FB86-4BDA-8ADA-871E22659204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE4F282-5A08-4866-81A2-D257AB1B857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="227">
   <si>
     <t>#Selling #Payment 
 Kunga — licensed PSP 
@@ -947,12 +947,1508 @@
   <si>
     <t>label</t>
   </si>
+  <si>
+    <t>💬 Onpayment — надежный партнер для мерчантов и провайдеров
+🍑 Компания приглашает к сотрудничеству по широкому спектру платежных направлений, преимущество работы с нами: 
+🔄 Полная автоматизация P2P-приема платежей
+✅ Простая и интуитивно понятная документация к API
+➡️ Поддержка ключевых направлений: C2C, СБП, QR-коды, трансграничные и банковские переводы, мобильная коммерция и др.
+➕ Автоматизированные выводы средств через личный кабинет
+💎 Удобная мерчант-панель для управления операциями, монитор</t>
+  </si>
+  <si>
+    <t>🔴Подключаю на площадки 
+🔴КА/ Ферма / БТ / МОБКОМ/ Госки / QR НСПК / Любое ГЕО
+🔴Дадим мануалы для любого метода работы 
+🔴За подключением: @Skrytgmakdak_TL</t>
+  </si>
+  <si>
+    <t>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная сс</t>
+  </si>
+  <si>
+    <t>🤑**Подключение на** **RosPlat вместе с НЕУЯЗВИМЫМИ**
+🛍**Ставки:**
+⏺** 100-999 ****👉****15%**
+⏺** 1000-4999 ****👉****11%**
+⏺** 5000-19999 ****👉****9%**
+⏺ **от 20000 ****👉****7,5%**
+🪙**Выплаты ( доступны сразу )**
+** **⏺**100-999 ****👉****5%**
+** **⏺**1,000-1,999 ****👉****3%**
+** **⏺**2,000-4,999 ****👉****2%**
+** **⏺**5,000-9,999 ****👉****1%**
+** **⏺**10,000-300,000 ****👉**** 0-1%**
+😄**Контр-Агенты:**
+⏺ **3,000-300,000** 👉**8%**
+**Условия страховых депозитов:**
+⏺** НА ВСЕ ЧЕКИ ****👉****1</t>
+  </si>
+  <si>
+    <t>Cigarette Payment Company！
+The payment company is seeking highly capable bank card merchants from all countries around the world.
+As long as you have sufficient bank cards and USDT, you will be able to earn a commission of over 2000 USDT per day.
+manner of working：
+You provide your bank card, and I will transfer funds into your card. Then you will issue USDT to me.
+This way, you can earn commissions from it.
+Fraudster, please go away. Our work requires a deposit as a guarantee.
+For the pooled fu</t>
+  </si>
+  <si>
+    <t>MobiusPay | White Label, который выдерживает рынок
+Вас заебали старые, кривые, проблемные технички?
+Системы, которые падают при нагрузке?
+WL, которые «вроде есть», но не выдерживают реального трафика?
+Давайте честно.
+Большинство White Label на рынке — это:
+— перекрашенный шаблон
+— устаревшая архитектура
+— техподдержка “завтра посмотрим”
+— и ноль понимания, что такое реальный платёжный поток
+MobiusPay — это не витрина. Это рабочая машина.
+🔥 17+ лет разработки
+Мы не «собрали панель на коленк</t>
+  </si>
+  <si>
+    <t>Подключим новых провайдеров в каскад! 
+Методы:
+Классика (сбп/с2с) 
+• 1000 - 4999 
+• 5000 - 9999 
+• 10000+ 
+QR НСПК (стат/дин) 
+Дадим лучшие условия на рынке!</t>
+  </si>
+  <si>
+    <t>💎 **Premium All-Geo Payment Infrastructure**
+🌐 Every Key Market Covered: TJ 🇹🇯 UZ 🇺🇿 KG 🇰🇬 RU 🇷🇺 KZ 🇰🇿 GE 🇬🇪 TR 🇹🇷 IN 🇮🇳 PL 🇵🇱 DE 🇩🇪 ES 🇪🇸 LT 🇱🇹 MD 🇲🇩 UK 🇬🇧 IT 🇮🇹 RS 🇷🇸 AR 🇦🇷 MX 🇲🇽 NL 🇳🇱 CH 🇨🇭 LU 🇱🇺 DK 🇩🇰 CY 🇨🇾 AE 🇦🇪 FR 🇫🇷 MT 🇲🇹 PT 🇵🇹
+💳 Legal Entity RET + Fresh FTD Solutions
+⚡️ SEPA Instant + Smooth Approvals
+🔥 Retention That Actually Converts
+📞 **Priority Support Channel**
+✅ Upgrade your stack in 24h</t>
+  </si>
+  <si>
+    <t>😃FUNPAY😎
+🔥Актуальный оффер**__
+Формат работы: Фермы /__** **__Контрагенты__** **__/ Классика / Внутрибанк / БТ / Мобильная коммерция__** **__ __****__⚡__****__Pay In - от __7__ - __16__ %
+📈 Курс: красный гринекс__** 🪙 Страховой депозит: $600–800 + KYC (обсуждаемо)
+💲**__Чеки __**- **__от 100__** **__до 300.000₽__**
+💡 Наши преимущества:
+✅ Сильные ментора ✅ Полный функционал по фермам и контрагентам
+✅ Удобный интерфейс и гибкая регулировка чеков
+✅ Добавляем любой банк по вашему запросу
+✅ Кру</t>
+  </si>
+  <si>
+    <t>✌️ ZAVOD - там где стабильно!
+Быстро и оперативно подключу на сильнейшую площадку!
+Страховой депозит: 500 🪙
+⏺Белые треугольники: 15.5%
+⏺Мобильная коммерция: 14.5%
+⏺Классика ХЧ: 7.5%
+🔝 Большое количество Gambling трафика от прямых поставщиков.
+⏩ [ПОДКЛЮЧИТЬСЯ СЕЙЧАС](https://t.me/voshodtl) ⏪</t>
+  </si>
+  <si>
+    <t>Приветствуем всех единомышленников - нынешних и будущих партнёров . **🤝****
+С радостью спешим вам сообщить - что мы снова набираем PSP в каскад ,отправляйте ваш список решений Оперативно рассмотрим офферы Напоминаю - с нами зарабатывают ****💵****
+У нас онли ГЕМБЛА ****⚡️****
+Прямые мерчи, 100 + гео В РАБОТЕ ****🌏**</t>
+  </si>
+  <si>
+    <t>**Приветствуем** всех единомышленников - нынешних и будущих партнёров . **🤝****
+С радостью спешим вам сообщить - что мы снова набираем PSP в каскад ,отправляйте ваш список решений Оперативно рассмотрим офферы Напоминаю - с нами зарабатывают ****💵****
+У нас онли ГЕМБЛА ****⚡️****
+Прямые мерчи, 100 + гео В РАБОТЕ ****🌏**</t>
+  </si>
+  <si>
+    <t>MobiusPay ищет мерчантов под мобильную коммерцию. 
+📱 Мобильный коммерция 
+✅ Отличная выдача - более 50 000$ ежедневно 
+⚡️ Быстрая обработка
+🤝 Инхаус команда
+Только геймбет
+Обработка стабильная. 
+Подключение быстрое — старт сразу после согласования. 
+Тип трафика — геймбет. 
+📩 В ЛС.
+@mobius_ceo</t>
+  </si>
+  <si>
+    <t>💎 **Premium All-Geo Payment Infrastructure**
+🌐 Every Key Market Covered: TJ 🇹🇯 UZ 🇺🇿 KG 🇰🇬 RU 🇷🇺 KZ 🇰🇿 GE 🇬🇪 TR 🇹🇷 IN 🇮🇳 PL 🇵🇱 DE 🇩🇪 ES 🇪🇸 LT 🇱🇹 MD 🇲🇩 UK 🇬🇧 IT 🇮🇹 RS 🇷🇸 AR 🇦🇷 MX 🇲🇽 NL 🇳🇱 CH 🇨🇭 LU 🇱🇺 DK 🇩🇰 CY 🇨🇾 AE 🇦🇪 FR 🇫🇷 MT 🇲🇹 PT 🇵🇹
+💳 Legal Entity RET + Fresh FTD Solutions
+⚡ SEPA Instant + Smooth Approvals
+🔥 Retention That Actually Converts
+📞 **Priority Support Channel**
+✅ Upgrade your stack in 24h</t>
+  </si>
+  <si>
+    <t>🌍 International Payment Gateway &amp; Payment Proxy Solutions
+💳 Pay-in &amp; Pay-out Services
+💸 USDT Settlement
+⚡ Fast Response &amp; Stable Settlement
+🔗 Manual / API Integration Supported
+✅ Small-Amount Testing Available
+🤝 Long-Term Cooperation Welcome
+🌎 Supported Countries &amp; Regions:
+🇮🇩 Indonesia | 🇻🇳 Vietnam | 🇵🇭 Philippines | 🇧🇷 Brazil
+🇯🇴 Jordan | 🇨🇱 Chile | 🇲🇾 Malaysia | 🇯🇵 Japan
+🇵🇪 Peru | 🇲🇳 Mongolia | 🇮🇶 Iraq | 🇲🇽 Mexico
+🇹🇷 Turkey | 🇲🇦 Morocco | 🇧🇩 Bangladesh
+🇹🇯 Tajikistan | 🇦🇪 UAE | 🇨🇴 Colomb</t>
+  </si>
+  <si>
+    <t>🔥 **All-in-One Platform Built to Dominate**🔥
+📈 Conquer Forex, Crypto, Arbitrage, CFD &amp; Recovery
+🧠 AI-powered monitoring &amp; advanced reporting
+💬 CRM with built-in chat + WhatsApp sync
+🌐 **Your own branded website included at no cost**
+🔐 Full VOIP, VPN &amp; RDP support unlocked
+💳 Direct PSP + bank connections from day one
+⚡️ **Go live in just 72 hours profits waiting!**</t>
+  </si>
+  <si>
+    <t>👨‍💻 Приветствуем всех!👨‍💻
+💼 Условия подключения:
+• 💳 СБП / карты / номер счёта / моб ком / нспк
+• ⚙️ Автоматика: под любые банки
+• 🧩 Поддержка: помощь от нашей команды на всех этапах
+💵 Условия по курсам:
+По курсу Rapira:
+• pay-in → 👨‍💻 
+__Классика для трейдеров:
+- От 1к до 5к  - 10% (100$ страховой)
+- От 5к до 10к - 9,5% (150$ страховой)
+- От 10к - 8,5% (200$ страховой) __
+__Мобком для трейдеров:
+от 100 до 10к - 14% (100$ страховой)
+НСПК для трейдеров:
+от 1к до 50к - 12% (150$ страховой__</t>
+  </si>
+  <si>
+    <t>💴** Принимайте криптоплатежи без комиссий** **и KYC**
+Криптопроцессинг для бизнеса: USDT, USDC, SOL TRON, BNB и другие.
+- 0% комиссии
+- Без KYC и бюрократии
+Подходит для интернет-магазинов, услуг, фриланса - любого бизнеса, который хочет принимать крипту напрямую, без посредников и процентов
+[@crucashru](https://t.me/+FQnYOh8OCOI1ODJk)</t>
+  </si>
+  <si>
+    <t>#selling #Payment 
+EU SEPA forex transfers - multiple acc types | flexible MDR | low KYC | in house UBO &amp; accs | 95% success | low/high risk 🫡✨</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk 
+☄️В активном поиске новых команд по Узбекситану
+🌐https://skyphoenix.info
+🙂SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>#crm 🚀 All-in-one solution for Forex &amp; Crypto brokers: PSP, CRM, telephony, call-center tools and live traffic. One provider, one ecosystem. DM us for a demo and pricing.</t>
+  </si>
+  <si>
+    <t>Working with operators, aff., media buyers and PSPs across 30+ GEOs. We provide performance traffic (Meta, PPC, Infl., TG) as well as payment solutions - fiat-crypto settlements and OTC services 🚀</t>
+  </si>
+  <si>
+    <t>⚡ High-speed platform and turnkey core built for brokers.
+🚀 Robo Core – CRM and trading platform single source code.
+⚙️ Engine Power – Native EA and execution high speed no crash.
+💳 Native Payments – In-house Crypto payments, wallets.
+🔒 Flat Monthly Pricing – No revenue share. No hidden fees. 
+📩 Message us right now to schedule a live demo.</t>
+  </si>
+  <si>
+    <t>ATpay Global Payments
+The payment company is seeking highly capable bank card merchants from all countries around the world.
+As long as you have sufficient bank cards and USDT, you will be able to earn a commission of over 2000 USDT per day.
+manner of working：
+You provide your bank card, and I will transfer funds into your card. Then you will issue USDT to me.
+This way, you can earn commissions from it.
+Fraudster, please go away. Our work requires a deposit as a guarantee.
+🇸🇬Singapore 🇲🇾Malaysi</t>
+  </si>
+  <si>
+    <t>**Sell 🏆**
+📈 PSP-Deposit/Charge/Recovery/EX-Deposit/Ret/Ftd/New Signups
+🎯 CA/EUROPE EN-NATIVE/US/AU/LATAM/RU</t>
+  </si>
+  <si>
+    <t>**Приветствуем всех единомышленников - нынешних и будущих партнёров . ****🤝****
+С радостью спешим вам сообщить - что мы снова набираем PSP в каскад ,отправляйте ваш список решений Оперативно рассмотрим офферы Напоминаю - с нами зарабатывают ****💵****
+У нас онли ГЕМБЛА ****⚡️****
+Прямые мерчи, 100 + гео В РАБОТЕ ****🌏**</t>
+  </si>
+  <si>
+    <t>💴** Принимаете платежи в бизнесе? Добавьте крипту без комиссий**
+Криптопроцессинг для бизнеса: USDT, USDC, SOL TRON, BNB и другие.
+- 0% комиссии
+- Без KYC и бюрократии
+Подходит для интернет-магазинов, услуг, фриланса - любого бизнеса, который хочет принимать крипту напрямую, без посредников и процентов
+[@crucashru](https://t.me/+FQnYOh8OCOI1ODJk)</t>
+  </si>
+  <si>
+    <t>Подключаем к Payscrow на любое направление.
+Выдаем бесплатно мануалы для работы, есть возможность работы без страхового депозита.</t>
+  </si>
+  <si>
+    <t>#selling #Payment 99% approval for your ftds ‼️
+Weekly settlement Instant setup ✅
+Link or integration ✅</t>
+  </si>
+  <si>
+    <t>**🎰 Hi everyone! 👋
+🚀 We build crypto iGaming platforms including:
+🎰 Casino
+⚽ Sportsbook
+👛 Crypto Wallet System
+🛠️ Admin Panel
+🤝 Referral &amp; Agent System
+💳 Crypto Payment Integration
+Our team delivers platforms that are:
+⚡ Fast &amp; Scalable
+🔒 Secure
+📱 Mobile-Friendly
+🛡️ KYC Ready
+🎯 Responsible Gaming Compliant
+🔌 Integrated with Leading Game Providers
+Whether you're launching a new crypto casino or upgrading an existing platform, we're here to help.
+📩 DM me if you're planning to build or sc</t>
+  </si>
+  <si>
+    <t>Доступны все 3D-шлюзы, доступна SAR-ссылка, мгновенные выплаты, работа с Apple Pay, работа с GPay, Visa, Mastercard, Amex, Discover, работа с платежными шлюзами в Великобритании, Дубае, Канаде, Австралии и Индии, работа с AED</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk 
+☄️В активном поиске новых команд по Южной Корее
+🌐https://skyphoenix.info
+🙂SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>❗️**Актуальный оффер JetPay **
+**Методы и ставки:**
+**Pay-Out:**
+**Курс: Rapira +1%**
+Холд выплаты до 120 минут.
+Предоставление чека в формате PDF 
+Выплата до двух чеков.
+**Pay-In**
+**C2C / СБП**
+• от 1 000 ₽ до 5 000 ₽ — 12%
+• от 5 000 ₽ до 10 000 ₽ — 11%
+• от 10 000 ₽ и выше — 9.5%
+**Монобанки**
+• от 1 000 ₽ и выше — 7.5%
+**Мобильная коммерция**
+• от 100 ₽ и выше — 15%
+**• Трафик с чеками **
+1000-9999 8.5%
+10000+ 7%
+Прямое подключение - @JetPay_Production</t>
+  </si>
+  <si>
+    <t>🔤🔤🔤- Auto Payment System
+Мы международный платежный шлюз по обработке платежей high-risk проектов
+Гео, по которым можем предложить обработку:
+🇨🇳 Китай
+🇵🇪 Перу
+🇹🇳 Тунис
+🇮🇩 Индонезия
+🇦🇷 Аргентина
+🇪🇨 Эквадор
+🇮🇳 Индия
+🇹🇷 Турция
+🇨🇴 Колумбия
+🇵🇰 Пакистан
+🇰🇷 Южная Корея
+🇧🇴 Боливия
+🇪🇬 Египет
+🇺🇿 Узбекистан
+🇹🇿 Танзания
+🇨🇱 Чили
+🇨🇩 Конго
+🇧🇩 Бангладеш
+🇵🇾 Парагвай
+Также рассмотри любые другие гео и найдём решение под вас!
+По поводу сотрудничества писать: @apshbdm</t>
+  </si>
+  <si>
+    <t>Есть** **много трафика с PDF-чеками от конечников (много мерчей) - проставим под метчинг на вашу платежку (10кк+ свободного). 
+Есть прямые казино-мерчанты, поставим на обработку площадке с репутацией. 
+Нужны прямые мерчанты и агрегаторы по СНГ, экзотике и Европе. 
+Заберем Вьетнам QR 
+Примем Ваш трафик — пишите с предложениями. 
+Нужна эмиссия Узбекистан 🇺🇿 
+Бесконечная приемка, заберем любой объем</t>
+  </si>
+  <si>
+    <t>Hi everyone! My name is Artem — I'm in business development at MoneyMania, a payment aggregator for iGaming/betting in Africa.
+We cover mobile money and local APMs across 15+ GEOs: Kenya, Nigeria, Tanzania, Ghana, Uganda, Zambia, Ivory Coast, Senegal, Rwanda, Botswana, DRC, Malawi, Gambia and others. Fast onboarding, competitive Pay-in/Pay-out rates, settlements in USDT. Fiat balance, no rolling reserve, high conversion, and the ability to accept** P2P payments in African countries (Ivory Coast</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk ☄️В активном поиске новых команд по Узбекистану 🌐https://skyphoenix.info
+🙂@SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>🟢 **SwipePay открывает набор на МОБИЛЬНУЮ КОМЕРЦИЮ В КРУГ ♻️ 
+**🤝 **Предоставим **полное сопровождение под ключ и работу в круг.
+✅ Персональный ментор 24/7 и актуальные методы работы. 
+✅ ЛЮБОЙ ОБЪЕМ ВЫПЛАТ 
+✅ Минимальный рабочий и Страховой депозит 500$ 
+Места ограничены: 
+🎙 @Roby_SwipePay
+🎙 @SwipePay</t>
+  </si>
+  <si>
+    <t>Estuary — автоматизированный приём платежей для high risk на базе p2p. Работаем с 2023 года.
+Почему мы:
+✅ Комиссии от 9% (индивидуально)
+✅ Подключение за 1 день
+✅ 7 секунд на транзакцию
+✅ Non dispute system — без диспутов
+✅ Каскадная система — конверсия выше
+✅ Вывод USDT без задержек
+✅ Поддержка 24/7 (ответ за 54 сек)
+✅ 20+ ГЕО по запросу
+✅ Кастомизация платёжного окна
+Доступно: РФ, Казахстан, Беларусь, Узбекистан, Турция и другие.
+Напишите — получите индивидуальные условия 🤝</t>
+  </si>
+  <si>
+    <t>All 3d gateway available, SAR link available Instant payout Apple pay work available, GPay work available, Visa Master card,Amex Discover work available, Uk Dubai Canada Australia India gateway available, AED work available,</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk 
+☄️В активном поиске новых команд по Азербайджану 
+🌐https://skyphoenix.info
+🙂SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>Usdt/Usdc payment gateway 0.4%/0.1% now for this month of merchants</t>
+  </si>
+  <si>
+    <t>**Подключу на PAYSCROW
+А-А внутри-банк,моб.коммерцию, КА, классика РФ, трансгран.
+Только актуальные методы работы, менторы и саппорты будут сопровождать в течении всей работы, помогут разобраться с площадкой.
+За подключением **@daviddavidsn</t>
+  </si>
+  <si>
+    <t>**🎰 Looking to Launch or Scale a Crypto iGaming Platform? 🚀
+We help businesses build modern, secure, and scalable iGaming platforms from the ground up — or upgrade existing casino and sportsbook products.
+🔥 What we can build &amp; integrate:
+🎰 Online Casino Platform
+⚽ Sportsbook &amp; Live Betting
+👛 Crypto Wallet &amp; Balance System
+💳 Crypto Payment &amp; Deposit/Withdrawal Integration
+🛠️ Powerful Admin &amp; Backoffice Panel
+🤝 Affiliate, Referral &amp; Agent Systems
+🎁 Bonus, VIP &amp; Loyalty Features
+📊 Player Management</t>
+  </si>
+  <si>
+    <t>#selling #psp EU UK AU payments , start testing today. Works flawlessly for ret,rec,ftds.</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk 
+☄️В активном поиске новых команд по Казахстану
+🌐https://skyphoenix.info
+🙂SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>Hey guys! Arquen Finance here! 
+Let me know if you need virtual cards 
+Funding: USDT, USDC
+We have cards in: EUR, USD, GBP 
+Apple Pay ✅ Google Pay ✅
+Delivery: API 
+White Label available</t>
+  </si>
+  <si>
+    <t>🔥 **Оффер для трейдеров — подключение к OzarkPay**
+💳 **Направление:** классика СБП / C2C
+🎰 **Трафик:** Gambling
+📈 **Ставка на вход:** 9%
+🛡 **Страховой депозит:** 500 USDT
+💰 **Рабочий депозит:** от 1 000 USDT
+💵 **High Check:** от 10 000 ₽
+⚡ Быстрое подключение к платформе
+📊 Прозрачная работа по заявкам и балансам
+🤝 Оперативная поддержка на всех этапах
+🚀 Готовность к запуску сразу после подключения и внесения депозитов</t>
+  </si>
+  <si>
+    <t>🔥 SkyPhoenix — платёжный партнёр для High-Risk 
+☄️В активном поиске новых команд по Узбекситану
+🌐https://skyphoenix.info
+🙂@SkyPhoenix_Valeria_KAM</t>
+  </si>
+  <si>
+    <t>✌️ ZAVOD - там где стабильно!
+Быстро и оперативно подключу на сильнейшую площадку!
+Страховой депозит: 500 🪙
+⏺Белые треугольники: 15.5%
+⏺Мобильная коммерция: 14.5%
+⏺Классика ХЧ: 7.5%
+👑 Большое количество Gambling трафика от прямых поставщиков.
+⏩ [ПОДКЛЮЧИТЬСЯ СЕЙЧАС](https://t.me/voshodtl) ⏪</t>
+  </si>
+  <si>
+    <t>🐫 **СameL****🐫****подключает к ****🦅**** Payscrow** 🦅
+Быстрый старт • Актуальные направления • Поддержка 24/7
+━━━━━━━━━━━━━━━
+🖥 **МАНУАЛЫ ПОД ВАШУ КОМАНДУ**
+Подберём и выдадим лучшие связки под ваш запрос 🐫
+📌 Доступны направления:
+• Внутрибанк
+• Мобильная коммерция
+• Контрагенты
+• Белые треугольники
+• Фермы
+• Гос
+• Залив
+━━━━━━━━━━━━━━━
+💸 **МЕТОДЫ И УСЛОВИЯ****🦅**
+📍 Все актуальные направления в работе
+📍 Курс: **RAPIRA + 1%**
+🐫 **Залив (Межбанк)**
+• 0₽ – 999₽ — 13%
+• От 1000₽ — 8.5%
+• От 5</t>
+  </si>
+  <si>
+    <t>At Nexxent, we prefer **"Payment Approved."** ✅
+Here's how we help you keep more revenue where it belongs:
+💳 Higher payment approval rates
+🔐 Secure in-house accounts
+📈 Solutions for both high-risk and standard businesses
+⚡️ Fast onboarding with flexible KYC
+Send me a message or connect with **@NexxentGeorge**.</t>
+  </si>
+  <si>
+    <t>Who need ftd ⁉️
+Selling ready ftd ‼️
+☎️ (ftd data, chargebacks, recovery, big depositors too available) 🔮
+Prepay only ✅</t>
+  </si>
+  <si>
+    <t>**GAMBLING ADS**
+АГЕНТСТВО WEFUN ПРЕДОСТАВЛЯЕТ
+👉 Аккаунт BM2500 — чистый, новый
+👉 Лимит расходов в день: 250$, 1500$, Безлимит
+👉 Рекламный аккаунт СТАРЫЙ и имеет сильную историю
+👉 Бесплатная ЗАМЕНА рекламного аккаунта при блокировке
+👉 Поддержка 24/7
+👉 Без скрытых комиссий
+✅ Все часовые пояса (часовой пояс +2, +3 всегда доступен)
+🏓 Азартные игры 📦Дропшиппинг 💵Крипта 🎰Казино 💰Инвест
+💰 Быстрое пополнение
+💰 ОПЛАТА: USDT, BTC, ETH, Payoneer, Wise
+WEFUN AGENCY PROVIDES
+✅ BM2500 Account – Clean, New – Smooth and Stable Delivery
+✅ Spend limit daily will be 250$, 1500$, Nolimit
+✅ Ads Account is OLD and have strong Spend history
+✅ Free REPLACE Ads Account when Ban
+✅ Support 24/7
+✅ No hidden fees
+✅ All timezones accepted (Time zone +2, +3 always available)
+💊 Nutra 🏓Gambling 📦Dropshipping 💵Crypto 🎰Casino 💰Invest
+💰 Fast Top up
+💰 PAY: USDT, BTC, ETH, Payoneer, Wise
+#WeFunagency | #Meta
+🏠 Ads account rental service:
+📩 For all questions : @meuth_wefunagency | @ceuth_agency
+📩 Please subscribe to the channel: @wefun_agency</t>
+  </si>
+  <si>
+    <t>Hey guys! Arquen Finance here! 
+Let me know if you need virtual cards 
+Funding: USDT, USDC
+We have cards in: EUR, USD, GBP
+Delivery: API
+White Label on special terms available!</t>
+  </si>
+  <si>
+    <t>💎Forex crypto Base-premium leads awaits
+Available segments:
+🔹 Forex/crypto Chargeback
+🔹 Ready FTDS
+🔹 Depositors
+🔹 Recovery leads
+🔹 Registrations
+🔹 Live Recovery
+⚡ ALSO HAVE FLASH COINS
+🪙 Supporting;BEP20,ERC20, TRC20
+💰 COINS: BTC, USDT, ETH, SOLANA.
+♻️ Replacement support
+📬 DM to connect</t>
+  </si>
+  <si>
+    <t>❗️**DECRYPT ОБНОВЛЯЕТ СТАВКИ****❗️****
+**Трафик - чистый гембет**
+**
+✅Предоставляем подробные мануалы для качественной работы
+✅Помогаем быстро выйти на стабильный результат
+✅Помогаем на всех этапах
+🟡**МК**
+100**₽** - ∞ **→ 13.5%**
+🟡**СБП/С2С**
+**1.000₽ – 4.999₽ → 9.5%**
+**5.000₽ – 9.999₽ → 8.5%**
+**10.000₽ – 14.999₽ → 7.5%**
+**15.000₽ – 19.999₽ → 7%**
+**от 20.000₽ → 6.5%**
+🟡**ГУ**
+1.000**₽** - ∞ **→ 8.5%**
+🔒**Страховой депозит**
+• **100₽** - **10.000₽** — **500 $**
+• **От** **10.000₽** — **1000 $****
+За подключением: ****@Moryak_DecryptPay**</t>
+  </si>
+  <si>
+    <t>Welcome bro! Yes we provide that .</t>
+  </si>
+  <si>
+    <t>needs a large number of Indian customers
+Large daily demand for USDT
+🤩1 USDT = 115-150 Indian Rupees🤩
+🤩1 USDT = 115-150 Indian Rupees🤩
+🤩1 USDT = 115-150 Indian Rupees🤩
+🔥 Available Fund Types
+✔️Hacker Fund
+✔️Cash Deposits 
+✔️Equity Funds 
+✔️Mixed Funds 
+✔️Gaming Funds 
+Mixed Funds are only available for UPI/IMPS payments.
+Integrity/Security/Efficiency/Stability
+➖➖➖➖➖➖➖➖➖➖➖ 
+👍👍👍We are a large  company headquartered in Hong Kong, China, with a very strong position in the Indian payments market.
+Our company has a large team of 100 sales representatives to We handle this work and work with over 500 Indian clients. We also offer substantial monthly bonuses to those who deliver high volumes of work. Contact us, and we'll provide a video showcasing our office environment and robust order system. Whatever order you need, we can help you fulfill it, and our prices are among the highest in the market. 👍👍👍
+In addition, we select several Indian employees each month and reward them based on their performance. Since the company's inception, we have distributed 168 iPhones and generous cash bonuses.
+➖➖➖➖➖➖➖➖➖➖➖
+💳The more USDT you provide during the transaction, the more profits you earn💰
+If you don't have USDT to sell, please don't waste your time. If you really want to participate and earn money, please contact us.
+🫵🏼We urgently need long-term, stable partners! 🫵🏼
+Contact me and I will arrange a salesperson for you. 222
+✈️Telegram： @fcaa8888888
+✈️Telegram：@L850517
+✈️Telegram： @cjj135117
+✈️Telegram： @usdt66999999
+✅Telegram group： @abcinrtousdt</t>
+  </si>
+  <si>
+    <t>#Supply
+**✅ 【Huidu Escrow Verified Group Supply and Demand】** —————————————————————————— 
+**HUIDU #1️⃣2️⃣6️⃣ Fourstar Card Merchant &amp; USDT Exchange (5,000 USDT Deposit)**
+Business Introduction：
+Fourstar Card Merchant &amp; USDT Exchange
+Fourstar is a Bangladesh-based card merchant and USDT exchange service provider, offering reliable payment solutions for businesses and individuals.
+Our Services
+Public Cards
+Private Cards
+Corporate Cards
+USDT Exchange Solutions
+B2B USDT Exchange Services
+Private Card-Based USDT Transactions
+Instant Settlement Processing
+Payment Methods
+We support major Bangladeshi payment channels, including:
+bKash
+Nagad
+Rocket
+Why Choose Fourstar?
+Professional and experienced team
+Fast and secure transaction processing
+Instant settlement solutions
+Specialized expertise in the iGaming industry
+More than 1 year of industry experience
+Business Cooperation
+Telegram: @Fourstar12 
+@CEO_PAY00 @Aloneboy_7d @COBRA20008 
+We are committed to providing efficient, secure, and professional payment and exchange solutions tailored to the needs of our clients.
+GroupLink：https://t.me/+4fCkMfMWpZo3NDky</t>
+  </si>
+  <si>
+    <t>**Payment Solutions Across Emerging Markets 🌍**
+🇵🇭 Philippines | 🇮🇩 Indonesia | 🇻🇳 Vietnam | 🇵🇪 Peru | 🇨🇴 Colombia | 🇮🇳 India | 🇧🇩 Bangladesh | 🇵🇰 Pakistan | 🇧🇷 Brazil | 🇲🇽 Mexico | 🇹🇭 Thailand | 🇪🇬 Egypt
+We provide secure and reliable payment solutions for:
+• 🎮 iGaming
+• 🎲 BC Games
+• 📈 Forex &amp; Investment Platforms
+✅ Local payment methods
+✅ Fast payouts
+✅ Scalable payment infrastructure
+DM me if you need help 🤝
+@DavidSmilepayz777</t>
+  </si>
+  <si>
+    <t>Hello everyone. I provide payment solutions for India, Vietnam, the Philippines, Thailand, and Indonesia. Please contact me if you are interested. @goodpayst</t>
+  </si>
+  <si>
+    <t>Предоставим платежное решение для вашего интернет магазина, обменника, гемблинг проекта 
+Классика 
+Диплинк 
+Трансгрн 
+Бт с пдф чеками</t>
+  </si>
+  <si>
+    <t>💵 **Direct Payments for Forex, Crypto &amp; Recovery**
+No aggregators. No sub-agents. No unnecessary fees.
+**White Change works directly with your brand.**
+⚡️ T+0 settlement
+🌍 Europe &amp; LATAM
+💰 Fixed fees
+🚀 Fast setup
+💸 Payment solutions for FTD and RETENTION
+**One provider. Direct responsibility.**
+✉️ @WHITE_CHANGE_CRYPTO
+**SPONSORED**</t>
+  </si>
+  <si>
+    <t>PSP 🇮🇳India first-hand payment solution provider
+(P2P, P2C, H2H, UPI Intent)
+⚠️No need to fill in UTR
+1️⃣Igaming traffic
+2️⃣Forex traffic 
+💻DM:@Eternity_99</t>
+  </si>
+  <si>
+    <t>Silkpay — India Payment Provider
+🇮🇳iGaming &amp; Forex
+⚡️ UPI Intent &amp; H2H Mode
+DM @Amy_Silkpay for a demo and rates !</t>
+  </si>
+  <si>
+    <t>Declined payments? That's money saying, "Maybe next time." 💸
+At Nexxent, we prefer **"Payment Approved."** ✅
+Here's how we help you keep more revenue where it belongs:
+💳 Higher payment approval rates
+🔐 Secure in-house accounts
+📈 Solutions for both high-risk and standard businesses
+⚡️ Fast onboarding with flexible KYC
+Ready to give your payment processing an upgrade? Send me a message or connect with **@NexxentGeorge**.</t>
+  </si>
+  <si>
+    <t>#Selling #Payments
+💸Direct payment solutions for Forex brokers.
+Available in DE, IT, ES, FR &amp; LATAM (ARS).
+✉️ Let's discuss a potential partnership.</t>
+  </si>
+  <si>
+    <t>👋 Hello everyone, we are offering Wires Payments Solutions,
+✅ Vban -IBANs under Client Name Available in:
+🇫🇷 France | 🇱🇺 Luxembourg
+🇳🇱Netherlands | 🇵🇱Poland
+🇱🇹Lithuania | 🇨🇾 Cyprus
+🇬🇷Greece | 🇲🇹 MT | 🇩🇰 DK
+IBAN C2B (NO KYC) 
+🇨🇦 Canada (Interac)
+Support 09:00 - 21:00 (UTC +3)
+Settle up to 48H
+Dm for more details 🤝</t>
+  </si>
+  <si>
+    <t>Hey everyone! 👋
+I'm from Fenito.
+We provide local payment solutions for iGaming in CIS, Turkey, and Asia — T+0, USDT balance, any volumes, no hidden fees.
+We already work with Zooma, Playfortuna, and 1xbet — so we know how to build stable payment flows for top-tier operators.
+If you need a reliable solution — let's talk in DMs</t>
+  </si>
+  <si>
+    <t>#selling #Payment Psp for ftds!
+90%+ approval - au, NZ, eu and more 👌
+Weekly settlements , instant setup✅✅✅
+DM for more information‼️</t>
+  </si>
+  <si>
+    <t>👋 Hello everyone, we are offering Wire Payments Solutions,
+✅ Vban -IBANs under Client Name in EU SEPA 🇪🇺
+🇨🇦 Canada (Wire + swift)
+Support 09:00 - 21:00 (UTC +3)
+Settle up to 48H
+Dm for more details 🤝</t>
+  </si>
+  <si>
+    <t>Всем привет! 👋 Я представляю 24PayBase.
+Предоставляем P2P/P2C платежные решения для iGaming и других высокорисковых вертикалей. На данный момент доступны следующие гео:
+🇺🇦 Украина - Card P2P / Deeplink (Mono, Privat)
+🇮🇳 Индия - UPI / QR
+🇵🇰 Пакистан - Easypaisa, JazzCash, Raast QR
+🇦🇿 Азербайджан - P2P
+🇺🇿 Узбекистан - Humo, Uzcard, Payme, Click, Uzum
+🇧🇩 Бангладеш - bKash, Nagad
+🇧🇷 Бразилия - PIX
+🇦🇷 Аргентина - CVU/CBU
+✅ T+0 по большинству гео
+✅ Сеттл в USDT
+✅ H2H и Redirect-интеграции
+✅ Работаем с любым типом трафика
+Если интересно - пишите в личные сообщения, буду рад обсудить сотрудничество.</t>
+  </si>
+  <si>
+    <t>#selling #payments #forex 
+👋 Direct payments for Forex Brokers.
+💸 DE, IT, FR, ES, IE, NL, LT + Argentina 🇦🇷 . 
+💼 Same-day settlements.
+✉️ DM if you run the show.</t>
+  </si>
+  <si>
+    <t>👋 Hello everyone, we are offering Wires Payments Solutions,
+✅ Vban -IBANs under Client Name Available in:
+🇫🇷 France | 🇱🇺 Luxembourg
+🇳🇱Netherlands | 🇵🇱Poland
+🇱🇹Lithuania | 🇨🇾 Cyprus
+🇬🇷Greece | 🇲🇹 MT | 🇩🇰 DK
+IBAN C2B (NO KYC) 
+🇨🇦 Canada (Wire + interac)
+Support 09:00 - 21:00 (UTC +3)
+Settle up to 48H
+Dm for more details 🤝</t>
+  </si>
+  <si>
+    <t>Добрый день, коллеги!
+Предоставляем платежные решения для гемблинг-проектов в таких гео, как Кыргызстан, Армения и Аргентина.
+Готовы принимать и качественно обрабатывать ваш гемблинг-трафик, обеспечивая высокий уровень сервиса и стабильную работу платежей.
+Открыты к новым партнёрствам и готовы обсудить индивидуальные условия.
+За подробностями и предложениями — пишите в личные сообщения.
+Hello, colleagues!
+We provide payment solutions for gambling projects in key GEOs, including Kyrgyzstan, Armenia, and Argentina.
+We are ready to accept and process your gambling traffic with a high level of service, reliable payment processing, and stable operations.
+We are open to new partnerships and happy to discuss tailored conditions.
+For more details and partnership proposals, feel free to contact us via DM.</t>
+  </si>
+  <si>
+    <t>I have indian paying solutions like 
+UPI IMPS RTGS available for high risk FX CFD GAM with usdt settlement</t>
+  </si>
+  <si>
+    <t>💵Добрый день всем, мы P2P решение под хай-риск бизнес - Equaringo 💵
+Находимся в поиске трафика по РФ:
+1️⃣Карточные методы (C2C, СБП): чек 5000+; 10000+
+2️⃣Белые треугольники: чек 1000+
+3️⃣Мобильная коммерция: чек 1000+
+🔤Готовы работать как с прямыми мерчантами, так и с агрегаторами🔤
+⭐️Также работаем по таким гео: ЛАТАМ, ИНДИЯ, КОРЕЯ
+⏱Если есть хорошие предложения, то жду в лс: @equaringo_biz</t>
+  </si>
+  <si>
+    <t>#Supply
+**✅ 【Huidu Escrow Verified Group Supply and Demand】** —————————————————————————— 
+**Huidu Verified Escrow Group 3️⃣5️⃣ - StarPay | Payment Gateway - Deposit 5000usdt**
+⭐️ StarPay | Payment Gateway
+一、业务介绍 | Business Overview
+🏆 专注于为游戏平台、电商及企业提供安全、稳定、高效的支付解决方案。
+Providing secure, stable, and efficient payment solutions for gaming platforms, e-commerce, and businesses.
+🥇 深耕孟加拉支付市场，支持高并发、高成功率与极速结算。
+Specialized in Bangladesh payment infrastructure with high concurrency, high success rates, and fast settlement.
+🤝 StarPay 是您值得长期信赖的全球支付合作伙伴。
+StarPay is your trusted long-term global payment partner.
+---
+二、我们的优势 | Our Advantages
+🥇 孟加拉支付专家
+Bangladesh Payment Expert
+🥇 支持金额范围 | Supported Transaction Range
+• bKash：100–50,000 BDT
+• Nagad：100–50,000 BDT
+• Rocket：100–50,000 BDT
+🥇 通道成功率 | Channel Success Rate
+80%+ Success Rate
+稳定、高效的支付通道，确保更高的交易成功率。
+Stable and efficient payment channels with an 80%+ transaction success rate.
+🥇 USD 极速结算 | Instant USD Settlement
+Settlement Time: 0
+无需等待，实时完成 USD 结算。
+No waiting. Real-time USD settlement.
+🥇 高成功率 · 极速结算
+稳定通道，资金快速到账，满足高流量业务需求。
+High Success Rate · Fast Settlement
+Reliable channels with rapid settlement for high-volume businesses.
+🥇 7×24 小时服务 | 24/7 Service
+专业商务、客服及技术团队全天候在线。
+Professional business, customer support, and technical team always online.
+---
+三、支持地区 | Supported Regions
+🇧🇩 孟加拉国
+🇮🇳 印度
+🇵🇰 巴基斯坦
+🌏 更多国家持续接入中……
+Bangladesh • India • Pakistan • More Regions Coming Soon
+---
+📞 商务负责人 | Business Contact
+StarPay Payment Gateway
+Fast • Secure • Reliable
+📩 Telegram: @Star_09124
+👤 Admin: @Xynb10045
+**Escrow Group Link:**
+https://t.me/+qVy03Q3Dk344NzQ0</t>
+  </si>
+  <si>
+    <t>#ADS 
+1️⃣1️⃣1️⃣｜Asia’s Leading iGaming Provider
+Game API × Global White Label × China Payment Solutions
+😊More than a game provider — your trusted iGaming partner
+From platform setup and game integration to payment and operational support, we deliver complete solutions to accelerate your business growth.
+🩷❤🧡Why Partner With DB Gaming?
+✅Launch your iGaming brand with our all-in-one solution
+✅Sports, Live Casino &amp; more via seamless API integration
+✅Smart backend with real-time analytics
+✅Professional team with 24/7 technical support
+🚀Get your iGaming business live in just 7 days!
+➡2026 Launch Offer Now Available
+🤥Contact Us：@dbgmBot
+📱Game API Integration
+🌐Global White Label Solutions
+🔡China Payment Solutions
+🌐Website：www.dbgaming.com
+🔈We're Hiring
+🔔Careers：@dbgaminghr</t>
+  </si>
+  <si>
+    <t>#selling
+PSP solution 
+Norway / Germany / Uk / NL</t>
+  </si>
+  <si>
+    <t>Soclean Merchant, [10 Aug 2026 at 6:27:18 AM]:
+**Payment Solutions Across Emerging Markets 🌍**
+🇵🇭 Philippines | 🇮🇩 Indonesia | 🇻🇳 Vietnam | 🇵🇪 Peru | 🇨🇴 Colombia | 🇮🇳 India | 🇧🇩 Bangladesh | 🇵🇰 Pakistan | 🇧🇷 Brazil | 🇲🇽 Mexico | 🇹🇭 Thailand | 🇪🇬 Egypt
+We provide secure and reliable payment solutions for:
+• 🎮 iGaming
+• 🎲 BC Games
+• 📈 Forex &amp; Investment Platforms
+✅ Local payment methods
+✅ Fast payouts
+✅ Scalable payment infrastructure
+DM me if you need help 🤝
+@DavidSmilepayz777</t>
+  </si>
+  <si>
+    <t>**Payment Soluton**
+__Vietnam 🇻🇳、Indonesia 🇮🇩、Philippines 🇵🇭、__Pakistan 🇵🇰__、Brazil 🇧🇷、Colombia 🇨🇴、Peru 🇵🇪、Mexico 🇲🇽__
+⭐️iGaming
+⭐️Forex
+⭐️Whitelabel 
+⭐️iGaming Provider
+⭐️Prediction Market
+⭐️Forex without license</t>
+  </si>
+  <si>
+    <t>Hi everyone! 👋 I'm from 24PayBase.
+We provide P2P/P2C payment solutions for iGaming and other high-risk verticals. Our currently available geos are:
+🇺🇦 Ukraine - Card P2P / Deeplink (Mono, Privat)
+🇮🇳 India - UPI / QR
+🇵🇰 Pakistan - Easypaisa, JazzCash, Raast QR
+🇦🇿 Azerbaijan - P2P
+🇺🇿 Uzbekistan - Humo, Uzcard, Payme, Click, Uzum
+🇧🇩 Bangladesh - bKash, Nagad
+🇧🇷 Brazil - PIX
+🇦🇷 Argentina - CVU/CBU Mercado Pago P2P/P2C
+✅ T+0 settlement for most geos
+✅ Settlement in USDT
+✅ H2H and Redirect integrations
+✅ Any type of traffic is accepted
+If you're interested, feel free to send me a DM. I'd be happy to discuss potential cooperation.</t>
+  </si>
+  <si>
+    <t>Всем привет!
+Представляю платежную инфраструктуру для high-risk проектов.
+На сегодняшний день доступны локальные решения для:
+🇺🇿 Узбекистан — Humo, Uzcard (Pay-In / Pay-Out)
+🇰🇬 Кыргызстан — P2P Cards (Pay-In / Pay-Out)
+🇦🇲 Армения — FastShift, Telcell, P2P (Pay-In / Pay-Out)
+🇪🇬 Египет — локальные wallet-решения (Vodafone Cash, Etisalat Cash, Orange Cash, Instapay и др.)
+🇦🇷 Аргентина — Bank Transfer / CVU (Pay-In / Pay-Out)
+🇷🇺 Россия — SBP, C2C (Pay-Out)
+✔ Local Pay-In / Pay-Out
+✔ API / H2H Integration
+✔ Settlement в USDT
+Если сейчас ищете платежное решение для одного из этих GEO или планируете запуск нового рынка — пишите в личные сообщения. Обсудим ваш кейс и посмотрим, чем можем помочь</t>
+  </si>
+  <si>
+    <t>#Selling Hello!
+My name is Kirill, and I from Jupiter.
+We provide our own payment solutions for multiple GEOs, including:
+🇷🇺 Russia
+🇮🇳 India
+🇵🇰 Pakistan
+🇮🇩 Indonesia
+🇧🇴 Bolivia
+🇪🇨 Ecuador
+🇧🇷 Brazil
+🇦🇷 Argentina
+🇰🇷 South Korea
+🌎 Africa (Benin, Burkina Faso, Cameroon, DRC, Ghana, Ivory Coast, Kenya, Malawi, Nigeria, Rwanda, Senegal, Tanzania, Togo, Uganda, Zambia, South Africa)
+📩 DM me. Let's talk! 🚀</t>
+  </si>
+  <si>
+    <t>Hello!
+My name is Kyle, and I from Jupiter.
+We provide our own payment solutions for multiple GEOs, including:
+🇷🇺 Russia
+🇮🇳 India
+🇵🇰 Pakistan
+🇮🇩 Indonesia
+🇧🇴 Bolivia
+🇪🇨 Ecuador
+🇧🇷 Brazil
+🇦🇷 Argentina
+🇰🇷 South Korea
+🌎 Africa (Benin, Burkina Faso, Cameroon, DRC, Ghana, Ivory Coast, Kenya, Malawi, Nigeria, Rwanda, Senegal, Tanzania, Togo, Uganda, Zambia, South Africa)
+📩 DM me. Let's talk! 🚀</t>
+  </si>
+  <si>
+    <t>[08.08.2026 13:07] Genri Finex: ✍️✍️✍️✍️✍️✍️✍️✍️✍️✍️✍️
+Всех категорически приветствуем!
+Мы - платежная система FINEX 🎭
+🎭 В активном поиске сотрудничества, интересны конечные клиенты, мерчанты, агрегаторы, провайдеры по обработке трафика 🎭
+**Coverage**: 
+🇷🇺 Russia
+🇰🇿 Kazakhstan
+🇰🇬 Kyrgyzstan 
+🇺🇿 Uzbekistan
+🇦🇿 Azerbaijan
+🇺🇬 Uganda 
+🇬🇭 Ghana 
+🇰🇪 Kenya 
+🇳🇬 Nigeria 
+🇧🇫 Burkina Faso 
+🇬🇭 Cameroon 
+🇪🇬 Egypt 
+🇬🇳 Guinea 
+🇲🇼 Malawi 
+🇷🇼 Rwanda 
+🇿🇦 South Africa 
+🇹🇿 Tanzania
+🇮🇳 India 
+🇨🇮 Ivory Coast 
+🇯🇵 Japan 
+🇦🇷 Argentina 
+🇹🇷 Turkey 
+🇧🇷 Brazil 
+🇨🇴 Colombia 
+🇪🇨 Ecuador 
+🇵🇪 Peru 
+🇲🇽 Mexico 
+🇨🇱 Chile 
+🇬🇹 Guatemala 
+🇨🇷 Costa Rica 
+🇻🇳 Vietnam
+✍️✍️✍️✍️✍️✍️✍️✍️✍️
+🎭 В активном поиске трейдеров по следующим направлениям: 
+🇷🇺 Россия:
+Классика
+МК
+БТ с ПДФ
+БТ без ПДФ
+🇰🇿 Казахстан:
+Локал
+🇰🇬 Киргизстан:
+МК
+Наши преимущества: 
+🥂 **Собственные платежные решения **
+➕ **Удобный личный кабинет.** 
+⚡️**Быстрая интеграция по API.**
+🎙 **Гибкие форматы сотрудничества.**
+💰 **Оперативные выплаты.**
+✅ **Поддержка 24/7.**
+📊**Современный платежный интерфейс.**
+🔎 **Высокий уровень безопасности.**
+Напишите нам для более детального обсуждения условий.
+🎭 @Genrifinex 🎭</t>
+  </si>
+  <si>
+    <t>**#Supply**
+**No:** 0510
+**
+Supply Resource: BULLPAY Multi-Currency Payment Gateway &amp; Merchant Onboarding**
+**Resource Details:** **BULLPAY**, owned and operated by RynixSoft, provides multi-currency payment processing and merchant onboarding solutions for B2B businesses across India, Pakistan, and crypto markets.
+**INR Processing:** Supporting Pay-In at 6% + ₹6 and Pay-Out at 3% + ₹6 per transaction, with specialized Safe Withdrawal routes available.
+**PKR Processing:** Offering Pay-In through EasyPaisa at 7% and JazzCash at 6%, with Pay-Out at a 4% flat rate.
+**USDT Processing:** Supporting crypto Pay-In at 3% and Pay-Out at 1%, providing an additional settlement option for international businesses.
+**Merchant Services:** Currently accepting new merchant accounts with fiat and crypto processing solutions designed for B2B payment operations.
+**Contact: ** @lawrasur 
+@rynixsoft
+**Supply/Demand Resource on ****Huidu.in****: 
+****https://huidu.in/en/business/30037**
+❗️ **Please be careful to prevent fraud when cooperating with supply and demand resources. If you need a guaranteed transaction, please contact ****@HuiduEscrow****
+****🔥**** Join ****Huidu.io**** iGaming Prime Hub to enjoy the supply and demand resources, to be one of us, please contact ****@huidushivam**** ****@hdmangal**</t>
+  </si>
+  <si>
+    <t>Hello everyone!
+**FlashPay** provides local payment solutions for High Risk projects.
+Asia, SEA, LatAm, Africa, CIS, Oceania
+Interested? Send us a DM 📩</t>
+  </si>
+  <si>
+    <t>🚀 Hello everyone!
+FlashPay provides local payment solutions for High Risk industries with support for a wide range of GEOs 🌍
+Our solutions are available in the following regions:
+🌍 **MENA Region**
+🇸🇦 Saudi Arabia 🇦🇪 UAE
+🇧🇭 Bahrain 🇯🇴 Jordan 🇸🇾 Syria
+🌍 **Africa**
+🇪🇬 Egypt 🇳🇬 Nigeria 🇰🇪 Kenya
+🇹🇿 Tanzania 🇸🇳 Senegal 🇿🇲 Zambia
+🇨🇮 Ivory Coast 🇨🇲 Cameroon
+🇺🇬 Uganda 🇷🇼 Rwanda
+🌎 **Latin America**
+🇧🇷 Brazil 🇲🇽 Mexico 🇦🇷 Argentina
+🇨🇴 Colombia 🇨🇱 Chile 🇵🇪 Peru
+🇧🇴 Bolivia 🇻🇪 Venezuela
+🌏 **Asia**
+🇮🇳 India 🇮🇩 Indonesia 🇻🇳 Vietnam
+🇹🇭 Thailand 🇲🇾 Malaysia 🇰🇷 South Korea
+🇵🇰 Pakistan 🇲🇳 Mongolia
+🌍 **CIS &amp; Europe**
+🇦🇿 Azerbaijan 🇺🇿 Uzbekistan
+🇹🇷 Turkey 🇵🇱 Poland
+Looking for stable payment solutions for your project?
+We are ready to discuss cooperation and provide the most suitable payment solution for your GEO.
+📩 Feel free to contact us via DM!</t>
+  </si>
+  <si>
+    <t>Greetings from MACPAY! ❤️
+If you are looking for reliable gaming/foreign exchange payment solutions, please contact me via private message.
+Regions:
+South Korea | Vietnam | Indonesia | India | Brazil | Bangladesh | Ethiopia | Philippines | Côte d'Ivoire | Malaysia | Hong Kong</t>
+  </si>
+  <si>
+    <t>✍️✍️✍️✍️✍️✍️✍️✍️✍️✍️✍️
+Всех категорически приветствуем!
+Мы - платежная система FINEX 🎭
+🎭 В активном поиске сотрудничества, интересны конечные клиенты, мерчанты, агрегаторы, провайдеры по обработке трафика 🎭
+**Coverage**: 
+🇷🇺 Russia
+🇰🇿 Kazakhstan
+🇰🇬 Kyrgyzstan 
+🇺🇿 Uzbekistan
+🇦🇿 Azerbaijan
+🇺🇬 Uganda 
+🇬🇭 Ghana 
+🇰🇪 Kenya 
+🇳🇬 Nigeria 
+🇧🇫 Burkina Faso 
+🇬🇭 Cameroon 
+🇪🇬 Egypt 
+🇬🇳 Guinea 
+🇲🇼 Malawi 
+🇷🇼 Rwanda 
+🇿🇦 South Africa 
+🇹🇿 Tanzania
+🇮🇳 India 
+🇨🇮 Ivory Coast 
+🇯🇵 Japan 
+🇦🇷 Argentina 
+🇹🇷 Turkey 
+🇧🇷 Brazil 
+🇨🇴 Colombia 
+🇪🇨 Ecuador 
+🇵🇪 Peru 
+🇲🇽 Mexico 
+🇨🇱 Chile 
+🇬🇹 Guatemala 
+🇨🇷 Costa Rica 
+🇻🇳 Vietnam
+✍️✍️✍️✍️✍️✍️✍️✍️✍️
+🎭 В активном поиске трейдеров по следующим направлениям: 
+🇷🇺 Россия:
+Классика
+МК
+БТ с ПДФ
+БТ без ПДФ
+🇰🇿 Казахстан:
+Локал
+🇰🇬 Киргизстан:
+МК
+Наши преимущества: 
+🥂 **Собственные платежные решения **
+➕ **Удобный личный кабинет.** 
+⚡️**Быстрая интеграция по API.**
+🎙 **Гибкие форматы сотрудничества.**
+💰 **Оперативные выплаты.**
+✅ **Поддержка 24/7.**
+📊**Современный платежный интерфейс.**
+🔎 **Высокий уровень безопасности.**
+Напишите нам для более детального обсуждения условий.
+🎭 @Genrifinex 🎭</t>
+  </si>
+  <si>
+    <t>🚀 ZIPPAY Global Payments｜Global Payment Solutions
+🌍 One-Stop Global Payment Solution
+ZIPPAY provides stable, secure, and efficient payment solutions for global merchants, businesses, and platforms. We connect worldwide payment channels to help businesses expand into international markets with seamless payment acceptance and reliable settlement services.
+🔥 Featured Payment Solutions:
+🇺🇸 US Dollar Online Payment Channel
+✅ Support USD payment scenarios
+✅ Stable processing with high approval rates
+✅ Designed for global merchants and businesses
+✅ Professional payment solutions with technical support
+🇨🇴 Colombia PSE Local Online Payment
+✅ Native Colombian bank payment method
+✅ Fast and convenient local payment experience
+✅ Helping businesses enter the Latin American market
+✅ Reliable payment support for overseas expansion
+💳 More Global Payment Services:
+✅ Visa / MasterCard Payment Acceptance
+✅ Apple Pay / Google Pay Payments
+✅ Cash App Payment Channel
+✅ India UPI Native Payments
+✅ Global Collection &amp; Settlement Services
+Whether you are running a cross-border business, online platform, gaming, digital service, or global marketplace, ZIPPAY provides customized payment solutions to support your worldwide expansion.
+🚀 Connect Global Payments. Grow Your Business Without Borders.
+📩 Telegram Contact:
+✈️ @yindu884
+✈️ @zippay00005
+✈️ @Zippay00001
+✈️ @jkjk999999</t>
+  </si>
+  <si>
+    <t>🚀🚀🚀 ZIPPAY Global Payments 🚀🚀🚀
+🌍 Global Payment Solutions
+Providing secure, reliable, and high-capacity payment and settlement solutions for businesses worldwide.
+━━━━━━━━━━━━━━━━━━
+💳 Visa / Mastercard
+🇺🇸 US Payment Channels
+🇮🇳 India Native Payment Channels
+💳 Cash App Payment Channel
+💵 Global Settlement Services
+✅ Global Collections
+✅ Global Payouts
+✅ US Settlement Services
+✅ India Settlement Services
+✅ USDT Exchange &amp; Settlement
+Global payment customer volume (Category I and II)
+━━━━━━━━━━━━━━━━━━
+✅ Stable payment channels with high success rates
+✅ Fast and efficient settlement
+✅ High-volume transaction support
+✅ Multi-country payment coverage
+✅ Professional technical &amp; customer support
+✅ Enterprise-grade payment solutions
+✅ Competitive pricing for long-term partners
+━━━━━━━━━━━━━━━━━━
+🤝 Our Services
+✔️ Enterprise Payment Solutions
+✔️ Cross-Border Payments &amp; Settlement
+✔️ Business Partnerships
+✔️ Channel Partnerships
+━━━━━━━━━━━━━━━━━━
+✈️ Telegram
+@yindu884
+@zippay00005
+@jkjk999999</t>
+  </si>
+  <si>
+    <t>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс юз: rezhunozhem</t>
+  </si>
+  <si>
+    <t>🐫 CameL  подключит на TradeMO 🤩
+🤩 Общий трафик СБП + карты с уже готовыми решениями под залив и «ферму»:
+💰 0₽–1999₽ — 13%
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+💰 от 10.000₽ — 6%
+🔄 В круг: до 16,5% 🤩
+🔥 VIP SBP (только проверенные КА + высокий чек):
+💰 2001₽–4000₽ — 7,5%
+💰 от 4000₽ — 7%
+🔄 В круг: до 10,5% 🤩
+🏦 Альфа → Альфа (с подробными инструкциями):
+💸 Любая сумма — 6,5%
+🔄 В круг: до 9,5% 🤩
+📱 SIM-направление (мануал + бот откупа):
+💰 до 2000₽ — 13%
+🔄 В круг: до 16% 🤩
+📊 Единая сетка выплат по всем направлениям:
+▫️ до 15.000₽ — 3%
+▫️ 15.000₽–35.000₽ — 2%
+▫️ 35.000₽–70.000₽ — 2,5%
+▫️ 70.000₽–300.000₽ — 2%
+⏰ Prime Time бонус: +0,5–1% к профиту 🤩
+💱 Единый курс RUB:
+🤩 Рапира +1%
+🤩Первая строка
+🤩 Красный стакан
+🤩 Запуск ваших методов с полной поддержкой и сопровождением
+🤩 Уникальный маркетплейс мануалов «ТМетод»
+🐫 За подробностями — в ЛС  @cameltll 🐫</t>
+  </si>
+  <si>
+    <t>**🔥**** ПОДКЛЮЧИТЬСЯ К GO6 ****🔥****
+****🌐****Ставки:
+****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****⬇️****
+****➡️****16% чеки 100–999****🪙****
+****➡️****14% чеки 1 000–4 999****🪙****
+****➡️****12% чеки от 5 000****🪙****
+****➡️****8% на VIP чеки от 10 000****🪙****
+****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****⬆️****
+****😨****Выплаты - 2****🤍****
+****🛜**** Своим трейдерам предоставляю мануалы на моб ком, гу, физ карты
+****📣****Для связи - **
+**rezhunozhem
+Young_Knife
+Butterflly_Knife**</t>
+  </si>
+  <si>
+    <t>🤩 **Pay4Amg** 🤩
+📢**Pay in**(Сбп/С2С):
+🟠**1-5к - 13.5%**
+🟠**5-10к - 12.5%**
+🟠**10к+ - 10%**
+📢**Pay out**(Сбп/С2С):
+🟠**1% за все чеки** (Rapira)
+🟠**Трангсран огромные объемы**
+🟠**Моб коммерция - 16%**
+🟠**Любые монобанки**
+🟠**НСПК** (как мультик, так и ру)
+🟠**Качественные контрагенты**
+🟠**БТ с PDF чеками - 9.5%**
+📢**Новые гео** в работе:
+🇹🇯**Таджикистан**
+🇰🇿**Казахстан**
+🇻🇪**Венесуэла**
+🇺🇿**Узбекистан**
+🇦🇷**Аргентина**
+🇮🇳**Индия**
+🇪🇬**Египет**
+🇦🇿**Азербайджан**
+❕**По остальным гео уточнять, сможем добавить по запросу**
+⚡️**Огромные объемы** трафика, классный интерфейс, **поддержка 24/7** для каждого трейдера!
+✔️**Частые розыгрыши**, созвоны, личные менторы и **штатные тимлиды**, которые помогут вам работать с любым материалом и выжимать из него **максимум**
+❕Для тимлидов **пожизненный 1%** за приведенных трейдеров + **бонусы от меня**
+⚡️**KYC ДЛЯ РАБОТЫ НЕ НУЖЕН**
+**Работай с лучшими** - 🤩
+✈️**По поводу подключения** - @pay4amg_ceo</t>
+  </si>
+  <si>
+    <t>👋🎰🎭**Подключение к KingsmanPay**🎭😊♥️
+🔮 Классика➖
+🔴100 - 999₽ ➡️ **15%**
+🔴1.000 - 4.999₽ ➡️ **11%**
+🔴 5.000 - 9.999₽ ➡️ **10%**
+🔴10.000 - 29.999₽  ➡️ **8%**
+🔴30.000➕ ➡️ **7,2%**
+🔴Выход (СБП)➡️ **1%**
+📃Курс: Rapira 
+🚂 ГУ➖
+🔴1.000₽ - 10.000₽ ➡️ **11%**
+ 📃Курс Rapira
+☠️ Контр Агенты➖
+🔴Вход ➡️ **8%**
+🔴Выход ➡️ **1%**
+⬇️Мин чек 5.000₽
+⚡️Средний чек 8-18к
+🛜 Мобильная Коммерция➖
+✍️Рф:
+🔴100 - 15.000 ➡️ 15%
+🔴Выход (РФ) ➡️ **1%**
+✍️Трансгран Тадж:
+🔴Вход ➡️ **13%** 
+🌊 QR NSPQ QR Manager или платежная ссылка➖
+🔴1000 - 100.000 ➡️ 12%
+🔴100 - 999 ➡️ 15%
+👻 БТ ➖
+🔴1.000₽ - 5.000₽ ➡️ **16%**
+📃 Курс Rapira
+🎅Монобанки➖
+✍️🏦➡️🏦 Сбер-Сбер:
+🔴от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+✍️🇷🇺➡️🇷🇺 ВТБ - ВТБ:
+🔴 от 1.000₽ ➡️ **8%**
+📃Курс Rapira
+🌐Альтернативные ГЕО➖
+✍️🇦🇿Азербайджан:
+🔴Вход ➡️  **4%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+✍️🇰🇿Казахстан:
+🔴Вход ➡️ **4.5%**
+🔴Выход ➡️ **1%**
+📃Курс: XE+3
+🔗Страховые депозиты➖
+▶️БТ - 500$
+▶️РФ - 600$
+▶️Моб ком - 250$
+▶️AZN - 600$
+▶️KZ - 600$
+💬За подключением в лс</t>
+  </si>
+  <si>
+    <t>**GIRA &amp; PAY2PROFIT обновляют СТАВКИ**
+❗️Специально для своих выбила лучшие условия подключения👇
+**Классика, фермы, залив:**
+0-99к/сутки - 10.5%
+100к-199к/сутки - 11.5%
+от 200к/сутки - 12.5%
+❗️Высокие обороты - индивидуальная ставка
+**БТ:**
+12.5%
+❗️Стабильный оборот от 100к/сутки - повышенная ставка
+**МК:**
+15%
+Страховой депозит прогрессивный - 10% от суточного оборота
+**Минимальный страховой - 150$**
+Пиши сейчас - работай уже через 60 минут
+💌За подключением: @Gira_TL</t>
+  </si>
+  <si>
+    <t>🚨 **Pro-Level Platform + CRM Built to Crush the Market** 🚨
+⚡️ Flawless 24/7 performance &amp; full automation
+📈 Perfect for Forex, Crypto, CFD &amp; Recovery brands
+💳 Seamless PSP integration – more deposits, less hassle
+🌟 **Your own branded website FREE with every deal**
+🔥 Stop settling for average, level up NOW
+💥 **Everything you need is waiting in my bio**</t>
+  </si>
+  <si>
+    <t>☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - ☑️ **Подключение к Cube** 🙈
+🔮**C2C / СБП**
+🔴от 1к до 5к ➡️ 15% 
+🔴до 10к ➡️ 13% 
+🦋 **МЕЛКОЧЕК**
+🔴 до 1к ➡️ 17%
+☠️ **КОНТР-АГЕНТЫ** ➡️ 10%
+📝**QR НСПК**
+🔴до 5к ➡️ 16%
+🔴от 5к ➡️ 13%
+✍️огромные объемы трафика✍️
+🛒 **ЯНДЕКС ЧАЕВЫЕ** ➡️ 13%
+✈️ **МОБКОМ**
+🔴до 1к ➡️ 15%
+🔴от 1к ➡️ 15%
+🔴Выход ➡️ 2% 
+📃(Рапира, средн.по стакану) 
+👻БТ out ➡️ 2% 
+🪭OCT out  ➡️ 1%
+🌐 **ТРАНСГРАН** ➡️ 7%
+👑**Локальный трафик****➖**
+🇦🇿 Азербайджан ➡️ 5/1,5%
+🇦🇷 Аргентина ➡️ 4/1%
+🇧🇷 Бразилия ➡️ 0,5/0,5%
+🇪🇬 Египет ➡️ 5/2%
+🇰🇿 Казахстан ➡️ 7/2%
+🇰🇬 Кыргызстан ➡️ 4/1%
+🇲🇩 Молдова ➡️ 5/1,5%
+🇰🇷Южная Корея ➡️ 6/1%
+🇹🇷 Турция ➡️ 5/1,5%
+🇺🇿 Узбекистан ➡️ 1.5/2
+🕷️Страховой депозит: 500$
+🔗Апелляционный депозит: 500$
+💬За подключением в лс - rezhunozhem  Butterflly_Knife</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,16 +2456,112 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF3FB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDECEA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F7EC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E8F7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAD9D7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F0DA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6F0D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5D0CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -977,17 +2569,183 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -998,6 +2756,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E0CF95BB-0F15-4E1C-B062-8A1D7F86D61E}" name="Таблиця1" displayName="Таблиця1" ref="A1:B234" totalsRowShown="0">
+  <autoFilter ref="A1:B234" xr:uid="{E0CF95BB-0F15-4E1C-B062-8A1D7F86D61E}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8315DA39-87EF-4494-97D4-C61AA7B2A8EC}" name="text" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{D7ADBF95-5F3F-47F4-AA0F-A5124575E6A3}" name="label"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1263,8 +3032,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B234"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1274,136 +3047,136 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="388.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="288" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18">
@@ -1418,272 +3191,272 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:2" ht="288" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:2" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="52" spans="1:2" ht="360" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B53">
@@ -1691,31 +3464,31 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:2" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B57">
@@ -1723,103 +3496,103 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="7" t="s">
         <v>56</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:2" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:2" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:2" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B70">
@@ -1834,24 +3607,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B74">
@@ -1867,7 +3640,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="7" t="s">
         <v>74</v>
       </c>
       <c r="B76">
@@ -1883,382 +3656,1265 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="A78" s="7" t="s">
         <v>76</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:2" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:2" ht="360" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:2" ht="360" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
         <v>80</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:2" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="94" spans="1:2" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="95" spans="1:2" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="97" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
+    <row r="98" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
+    <row r="99" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="100" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+    <row r="101" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="102" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="103" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    <row r="104" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    <row r="105" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    <row r="106" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A106" s="8" t="s">
         <v>103</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    <row r="107" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A107" s="9" t="s">
         <v>104</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+    <row r="108" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="9" t="s">
         <v>105</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+    <row r="109" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="10" t="s">
         <v>106</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+    <row r="110" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="10" t="s">
         <v>107</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="111" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A111" s="10" t="s">
         <v>108</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="112" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
+    <row r="113" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A113" s="11" t="s">
         <v>110</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
+    <row r="114" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
         <v>111</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
+    <row r="115" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
         <v>112</v>
       </c>
       <c r="B115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="116" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="12" t="s">
         <v>113</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="117" spans="1:2" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A117" s="13" t="s">
         <v>114</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
+    <row r="118" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A118" s="13" t="s">
         <v>115</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
+    <row r="119" spans="1:2" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A119" s="13" t="s">
         <v>116</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
+    <row r="120" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="14" t="s">
         <v>117</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+    <row r="121" spans="1:2" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="14" t="s">
         <v>118</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
+    <row r="122" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
         <v>119</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+    <row r="123" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
         <v>120</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+    <row r="124" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="403.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="331.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="317.39999999999998" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A167" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="159" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="389.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="303" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A181" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="389.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="403.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="303" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="375" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="331.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A216" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A224" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A234" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B234">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>